--- a/data/planning.xlsx
+++ b/data/planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dairyconsultnl-my.sharepoint.com/personal/albart_dairyconsult_nl/Documents/Documenten/online_dingen/studiereis_italie/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="11_AD4DB114E441178AC67DF402B693FAF4693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70484B26-9FFD-4857-AD94-7A1F3EB91F33}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_AD4DB114E441178AC67DF402B693FAF4693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{967D1DD8-7AAE-440B-9BCE-9FF74B5964F5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>datum</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Aankomst bedrijf 3</t>
   </si>
   <si>
-    <t>Aankomst hotel</t>
-  </si>
-  <si>
     <t>Hotel Mantua</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
     <t>Vertrek naar Milaan</t>
   </si>
   <si>
-    <t>Aankomst in hotel</t>
-  </si>
-  <si>
     <t>Rondleiding Milaan</t>
   </si>
   <si>
@@ -109,6 +103,27 @@
   </si>
   <si>
     <t>vertrek naar huis</t>
+  </si>
+  <si>
+    <t>Piazza Sordello, 13 – 46100 MANTOVA</t>
+  </si>
+  <si>
+    <t>Viale Lombardia, 74  20131 Milan (Italy)</t>
+  </si>
+  <si>
+    <t>https://www.hotellombardia.com/</t>
+  </si>
+  <si>
+    <t>http://www.mantegnahotels.com</t>
+  </si>
+  <si>
+    <t>Aankomst Hotel Mantova</t>
+  </si>
+  <si>
+    <t>Aankomst in hotel Milaan</t>
+  </si>
+  <si>
+    <t>P.le Supercortemaggiore 4 - 20097 SAN DONATO MIL.SE (MI)</t>
   </si>
 </sst>
 </file>
@@ -116,9 +131,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +148,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Bierstadt Display"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,11 +176,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -479,8 +503,8 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
+      <c r="D2" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -580,10 +604,13 @@
         <v>0.75</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -597,7 +624,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -611,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -622,10 +649,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
         <v>19</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -647,10 +674,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
         <v>21</v>
-      </c>
-      <c r="D15" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -661,10 +688,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46324</v>
       </c>
@@ -672,10 +699,16 @@
         <v>0.75</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46324</v>
       </c>
@@ -683,10 +716,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46324</v>
       </c>
@@ -694,10 +727,10 @@
         <v>0.875</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46325</v>
       </c>
@@ -708,7 +741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46325</v>
       </c>
@@ -716,12 +749,13 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{22E0417F-3310-49E0-A17F-5E491840A44E}"/>
+    <hyperlink ref="E10" r:id="rId2" xr:uid="{1C051F95-5881-40D9-95A9-7C998F5A62BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/planning.xlsx
+++ b/data/planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dairyconsultnl-my.sharepoint.com/personal/albart_dairyconsult_nl/Documents/Documenten/online_dingen/studiereis_italie/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="11_AD4DB114E441178AC67DF402B693FAF4693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{967D1DD8-7AAE-440B-9BCE-9FF74B5964F5}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_AD4DB114E441178AC67DF402B693FAF4693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{432EF37B-C253-47D7-9774-121D64CDA13B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>datum</t>
   </si>
@@ -63,30 +63,15 @@
     <t>Aankomst</t>
   </si>
   <si>
-    <t>Bedrijf 1</t>
-  </si>
-  <si>
-    <t>Aankomst bedrijf 2</t>
-  </si>
-  <si>
     <t>Lunch</t>
   </si>
   <si>
-    <t>Aankomst bedrijf 3</t>
-  </si>
-  <si>
     <t>Hotel Mantua</t>
   </si>
   <si>
     <t>Mantua</t>
   </si>
   <si>
-    <t>Vertrek naar bedrijf</t>
-  </si>
-  <si>
-    <t>Bedrijf Rain360</t>
-  </si>
-  <si>
     <t>Bezoek bedrijf Cristella</t>
   </si>
   <si>
@@ -124,6 +109,36 @@
   </si>
   <si>
     <t>P.le Supercortemaggiore 4 - 20097 SAN DONATO MIL.SE (MI)</t>
+  </si>
+  <si>
+    <t>Bosetti Farm s.s.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ctw6gnPGfqC9efT3A</t>
+  </si>
+  <si>
+    <t>Bezoek aan CMP Impianti S.R.L.</t>
+  </si>
+  <si>
+    <t>https://www.cmp-impianti.it/</t>
+  </si>
+  <si>
+    <t>Il Cantinone Restaurant</t>
+  </si>
+  <si>
+    <t>https://ilcantinone.wixsite.com/ilcantinone</t>
+  </si>
+  <si>
+    <t>Bedrijf 2</t>
+  </si>
+  <si>
+    <t>Aankomst bedrijf met Rain360</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Z6ktJZd6t1p6GhVq7</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/cristellaholstein/</t>
   </si>
 </sst>
 </file>
@@ -470,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="8.7265625" style="3"/>
@@ -504,7 +519,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -543,7 +558,7 @@
         <v>46323</v>
       </c>
       <c r="B5" s="3">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -554,13 +569,16 @@
         <v>46323</v>
       </c>
       <c r="B6" s="3">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -568,10 +586,13 @@
         <v>46323</v>
       </c>
       <c r="B7" s="3">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -579,10 +600,16 @@
         <v>46323</v>
       </c>
       <c r="B8" s="3">
-        <v>0.5625</v>
+        <v>0.55208333333333337</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -590,10 +617,10 @@
         <v>46323</v>
       </c>
       <c r="B9" s="3">
-        <v>0.64583333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -604,13 +631,13 @@
         <v>0.75</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -624,7 +651,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -638,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -649,10 +676,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -660,10 +684,13 @@
         <v>46324</v>
       </c>
       <c r="B14" s="3">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -671,13 +698,10 @@
         <v>46324</v>
       </c>
       <c r="B15" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -685,10 +709,16 @@
         <v>46324</v>
       </c>
       <c r="B16" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -696,16 +726,10 @@
         <v>46324</v>
       </c>
       <c r="B17" s="3">
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -713,9 +737,15 @@
         <v>46324</v>
       </c>
       <c r="B18" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -724,21 +754,21 @@
         <v>46324</v>
       </c>
       <c r="B19" s="3">
-        <v>0.875</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B20" s="3">
-        <v>0.29166666666666669</v>
+        <v>0.875</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -746,16 +776,28 @@
         <v>46325</v>
       </c>
       <c r="B21" s="3">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B22" s="3">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C21" t="s">
-        <v>25</v>
+      <c r="C22" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{22E0417F-3310-49E0-A17F-5E491840A44E}"/>
     <hyperlink ref="E10" r:id="rId2" xr:uid="{1C051F95-5881-40D9-95A9-7C998F5A62BA}"/>
+    <hyperlink ref="E18" r:id="rId3" xr:uid="{BAD57670-E8E6-47D8-B7D5-F8F5E00A9C67}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
